--- a/data/raw/GLNPO 2024 Spring/Huron/D100/HU 48 D100 Spring 2024 24GH02I13 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Huron/D100/HU 48 D100 Spring 2024 24GH02I13 Zoop.xlsx
@@ -5,19 +5,22 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\GLNPO 2024 Spring\Huron\D100\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Huron\D100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7215A1DB-1E9A-4196-A2A9-7FAC3D2DF5BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF464213-A2E7-4430-BCCA-9016EBDB76E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B7EC3FBA-13EF-49DD-99E1-5755DB56AABA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7EC3FBA-13EF-49DD-99E1-5755DB56AABA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$239</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId2"/>
+    <pivotCache cacheId="37" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2964" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2966" uniqueCount="87">
   <si>
     <t>SAMPLENUM</t>
   </si>
@@ -5420,7 +5423,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A67746FE-ED2C-48D4-B4EF-E6CF2CAC3DE8}" name="PivotTable2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A67746FE-ED2C-48D4-B4EF-E6CF2CAC3DE8}" name="PivotTable2" cacheId="37" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="U1:AA19" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField showAll="0"/>
@@ -5882,20 +5885,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA400D11-AEBD-46C1-9BFD-0E6F8DC12898}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AA239"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="31.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="31.88671875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.88671875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="6" bestFit="1" customWidth="1"/>
     <col min="24" max="25" width="3" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="2.88671875" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5957,7 +5961,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -6031,7 +6035,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -6099,7 +6103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -6164,7 +6168,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -6232,7 +6236,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -6297,7 +6301,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -6362,7 +6366,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -6430,7 +6434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -6495,7 +6499,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -6560,7 +6564,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -6625,7 +6629,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -6693,7 +6697,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -6764,7 +6768,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -6832,7 +6836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -6894,7 +6898,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -6965,7 +6969,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -7033,7 +7037,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -7101,7 +7105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -7175,7 +7179,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -7228,7 +7232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -7290,7 +7294,7 @@
         <v>1.002</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -7350,7 +7354,7 @@
         <v>1.0029999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -7412,7 +7416,7 @@
         <v>0.999</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -7472,7 +7476,7 @@
         <v>0.996</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -7532,7 +7536,7 @@
       </c>
       <c r="W25" s="14"/>
     </row>
-    <row r="26" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -7592,7 +7596,7 @@
       </c>
       <c r="W26" s="14"/>
     </row>
-    <row r="27" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -7650,7 +7654,7 @@
       <c r="V27" s="13"/>
       <c r="W27" s="14"/>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -7703,7 +7707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -7756,7 +7760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -7809,7 +7813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -7862,7 +7866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -7915,7 +7919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -7968,7 +7972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -8021,7 +8025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -8074,7 +8078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -8127,7 +8131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -8180,7 +8184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -8233,7 +8237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -8286,7 +8290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -8339,7 +8343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -8392,7 +8396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -8445,7 +8449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -8498,7 +8502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -8551,7 +8555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -8604,7 +8608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -8657,7 +8661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -8710,7 +8714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -8763,7 +8767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -8816,7 +8820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -8869,7 +8873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -8922,7 +8926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -8975,7 +8979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -9028,7 +9032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -9075,13 +9079,13 @@
         <v>0.83799999999999997</v>
       </c>
       <c r="P54" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="Q54">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -9134,7 +9138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -9187,7 +9191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -9240,7 +9244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -9293,7 +9297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -9346,7 +9350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -9399,7 +9403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -9452,7 +9456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -9505,7 +9509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -9558,7 +9562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -9611,7 +9615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>18</v>
       </c>
@@ -9664,7 +9668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -9717,7 +9721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>18</v>
       </c>
@@ -9770,7 +9774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -9823,7 +9827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -9876,7 +9880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -9929,7 +9933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -9982,7 +9986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -10035,7 +10039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -10088,7 +10092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -10141,7 +10145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -10194,7 +10198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -10247,7 +10251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>18</v>
       </c>
@@ -10300,7 +10304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>18</v>
       </c>
@@ -10353,7 +10357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>18</v>
       </c>
@@ -10406,7 +10410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>18</v>
       </c>
@@ -10459,7 +10463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>18</v>
       </c>
@@ -10512,7 +10516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>18</v>
       </c>
@@ -10565,7 +10569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>18</v>
       </c>
@@ -10618,7 +10622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>18</v>
       </c>
@@ -10671,7 +10675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>18</v>
       </c>
@@ -10724,7 +10728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>18</v>
       </c>
@@ -10777,7 +10781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>18</v>
       </c>
@@ -10830,7 +10834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>18</v>
       </c>
@@ -10883,7 +10887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>18</v>
       </c>
@@ -10936,7 +10940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>18</v>
       </c>
@@ -10989,7 +10993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>18</v>
       </c>
@@ -11042,7 +11046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>18</v>
       </c>
@@ -11095,7 +11099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>18</v>
       </c>
@@ -11148,7 +11152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>18</v>
       </c>
@@ -11201,7 +11205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>18</v>
       </c>
@@ -11254,7 +11258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>18</v>
       </c>
@@ -11307,7 +11311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>18</v>
       </c>
@@ -11360,7 +11364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>18</v>
       </c>
@@ -11413,7 +11417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -11466,7 +11470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>18</v>
       </c>
@@ -11519,7 +11523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>18</v>
       </c>
@@ -11572,7 +11576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>18</v>
       </c>
@@ -11625,7 +11629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>18</v>
       </c>
@@ -11678,7 +11682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>18</v>
       </c>
@@ -11731,7 +11735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>18</v>
       </c>
@@ -11784,7 +11788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>18</v>
       </c>
@@ -11837,7 +11841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>18</v>
       </c>
@@ -11890,7 +11894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>18</v>
       </c>
@@ -11943,7 +11947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>18</v>
       </c>
@@ -11996,7 +12000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>18</v>
       </c>
@@ -12049,7 +12053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>18</v>
       </c>
@@ -12102,7 +12106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>18</v>
       </c>
@@ -12155,7 +12159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>18</v>
       </c>
@@ -12208,7 +12212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>18</v>
       </c>
@@ -12261,7 +12265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>18</v>
       </c>
@@ -12314,7 +12318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>18</v>
       </c>
@@ -12367,7 +12371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>18</v>
       </c>
@@ -12420,7 +12424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>18</v>
       </c>
@@ -12473,7 +12477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>18</v>
       </c>
@@ -12526,7 +12530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>18</v>
       </c>
@@ -12579,7 +12583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>18</v>
       </c>
@@ -12632,7 +12636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>18</v>
       </c>
@@ -12685,7 +12689,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>18</v>
       </c>
@@ -12738,7 +12742,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>18</v>
       </c>
@@ -12791,7 +12795,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>18</v>
       </c>
@@ -12844,7 +12848,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>18</v>
       </c>
@@ -12897,7 +12901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>18</v>
       </c>
@@ -12950,7 +12954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>18</v>
       </c>
@@ -13003,7 +13007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>18</v>
       </c>
@@ -13056,7 +13060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>18</v>
       </c>
@@ -13109,7 +13113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>18</v>
       </c>
@@ -13162,7 +13166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>18</v>
       </c>
@@ -13215,7 +13219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>18</v>
       </c>
@@ -13268,7 +13272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>18</v>
       </c>
@@ -13321,7 +13325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>18</v>
       </c>
@@ -13374,7 +13378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>18</v>
       </c>
@@ -13427,7 +13431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>18</v>
       </c>
@@ -13480,7 +13484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>18</v>
       </c>
@@ -13533,7 +13537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>18</v>
       </c>
@@ -13586,7 +13590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>18</v>
       </c>
@@ -13639,7 +13643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>18</v>
       </c>
@@ -13692,7 +13696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>18</v>
       </c>
@@ -13745,7 +13749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>18</v>
       </c>
@@ -13798,7 +13802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>18</v>
       </c>
@@ -13851,7 +13855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>18</v>
       </c>
@@ -13904,7 +13908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>18</v>
       </c>
@@ -13957,7 +13961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>18</v>
       </c>
@@ -14010,7 +14014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>18</v>
       </c>
@@ -14063,7 +14067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>18</v>
       </c>
@@ -14116,7 +14120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>18</v>
       </c>
@@ -14169,7 +14173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>18</v>
       </c>
@@ -14222,7 +14226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>18</v>
       </c>
@@ -14275,7 +14279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>18</v>
       </c>
@@ -14328,7 +14332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>18</v>
       </c>
@@ -14381,7 +14385,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>18</v>
       </c>
@@ -14434,7 +14438,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>18</v>
       </c>
@@ -14487,7 +14491,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>18</v>
       </c>
@@ -14540,7 +14544,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>18</v>
       </c>
@@ -14593,7 +14597,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>18</v>
       </c>
@@ -14646,7 +14650,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>18</v>
       </c>
@@ -14699,7 +14703,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>18</v>
       </c>
@@ -14752,7 +14756,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>18</v>
       </c>
@@ -14805,7 +14809,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>18</v>
       </c>
@@ -14858,7 +14862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>18</v>
       </c>
@@ -14911,7 +14915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>18</v>
       </c>
@@ -14964,7 +14968,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>18</v>
       </c>
@@ -15017,7 +15021,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>18</v>
       </c>
@@ -15070,7 +15074,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>18</v>
       </c>
@@ -15123,7 +15127,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>18</v>
       </c>
@@ -15176,7 +15180,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>18</v>
       </c>
@@ -15229,7 +15233,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>18</v>
       </c>
@@ -15282,7 +15286,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>18</v>
       </c>
@@ -15335,7 +15339,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>18</v>
       </c>
@@ -15388,7 +15392,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>18</v>
       </c>
@@ -15441,7 +15445,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>18</v>
       </c>
@@ -15494,7 +15498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>18</v>
       </c>
@@ -15547,7 +15551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>18</v>
       </c>
@@ -15600,7 +15604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>18</v>
       </c>
@@ -15653,7 +15657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>18</v>
       </c>
@@ -15706,7 +15710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>18</v>
       </c>
@@ -15759,7 +15763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>18</v>
       </c>
@@ -15812,7 +15816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>18</v>
       </c>
@@ -15859,13 +15863,13 @@
         <v>0.51600000000000001</v>
       </c>
       <c r="P182" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="Q182">
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>18</v>
       </c>
@@ -15918,7 +15922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>18</v>
       </c>
@@ -15971,7 +15975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>18</v>
       </c>
@@ -16024,7 +16028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>18</v>
       </c>
@@ -16077,7 +16081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>18</v>
       </c>
@@ -16130,7 +16134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>18</v>
       </c>
@@ -16183,7 +16187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>18</v>
       </c>
@@ -16236,7 +16240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>18</v>
       </c>
@@ -16289,7 +16293,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>18</v>
       </c>
@@ -16342,7 +16346,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>18</v>
       </c>
@@ -16395,7 +16399,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>18</v>
       </c>
@@ -16448,7 +16452,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>18</v>
       </c>
@@ -16501,7 +16505,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>18</v>
       </c>
@@ -16554,7 +16558,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>18</v>
       </c>
@@ -16607,7 +16611,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>18</v>
       </c>
@@ -16660,7 +16664,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>18</v>
       </c>
@@ -16713,7 +16717,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>18</v>
       </c>
@@ -16766,7 +16770,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>18</v>
       </c>
@@ -16819,7 +16823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>18</v>
       </c>
@@ -16872,7 +16876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>18</v>
       </c>
@@ -16925,7 +16929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>18</v>
       </c>
@@ -16978,7 +16982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>18</v>
       </c>
@@ -17031,7 +17035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>18</v>
       </c>
@@ -17084,7 +17088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>18</v>
       </c>
@@ -17137,7 +17141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>18</v>
       </c>
@@ -17190,7 +17194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>18</v>
       </c>
@@ -17243,7 +17247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>18</v>
       </c>
@@ -17296,7 +17300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>18</v>
       </c>
@@ -17349,7 +17353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>18</v>
       </c>
@@ -17402,7 +17406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>18</v>
       </c>
@@ -17455,7 +17459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>18</v>
       </c>
@@ -17508,7 +17512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>18</v>
       </c>
@@ -17561,7 +17565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>18</v>
       </c>
@@ -17614,7 +17618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>18</v>
       </c>
@@ -17667,7 +17671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>18</v>
       </c>
@@ -17720,7 +17724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>18</v>
       </c>
@@ -17773,7 +17777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>18</v>
       </c>
@@ -17826,7 +17830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>18</v>
       </c>
@@ -17879,7 +17883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>18</v>
       </c>
@@ -17932,7 +17936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>18</v>
       </c>
@@ -17985,7 +17989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>18</v>
       </c>
@@ -18038,7 +18042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>18</v>
       </c>
@@ -18091,7 +18095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>18</v>
       </c>
@@ -18144,7 +18148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>18</v>
       </c>
@@ -18197,7 +18201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>18</v>
       </c>
@@ -18250,7 +18254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>18</v>
       </c>
@@ -18293,8 +18297,8 @@
       <c r="N228" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="O228">
-        <v>0.625</v>
+      <c r="O228" t="s">
+        <v>38</v>
       </c>
       <c r="P228" t="s">
         <v>38</v>
@@ -18303,7 +18307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>18</v>
       </c>
@@ -18346,8 +18350,8 @@
       <c r="N229" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="O229">
-        <v>0.625</v>
+      <c r="O229" t="s">
+        <v>38</v>
       </c>
       <c r="P229" t="s">
         <v>38</v>
@@ -18356,7 +18360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="7" t="s">
         <v>18</v>
       </c>
@@ -18409,7 +18413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="7" t="s">
         <v>18</v>
       </c>
@@ -18462,7 +18466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="7" t="s">
         <v>18</v>
       </c>
@@ -18515,7 +18519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="7" t="s">
         <v>18</v>
       </c>
@@ -18568,7 +18572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="7" t="s">
         <v>18</v>
       </c>
@@ -18621,7 +18625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="7" t="s">
         <v>18</v>
       </c>
@@ -18674,7 +18678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="7" t="s">
         <v>18</v>
       </c>
@@ -18727,7 +18731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A237" s="7" t="s">
         <v>18</v>
       </c>
@@ -18780,7 +18784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A238" s="7" t="s">
         <v>18</v>
       </c>
@@ -18833,7 +18837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="7" t="s">
         <v>18</v>
       </c>
@@ -18887,6 +18891,14 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R239" xr:uid="{DA400D11-AEBD-46C1-9BFD-0E6F8DC12898}">
+    <filterColumn colId="10">
+      <filters>
+        <filter val="Leptodiaptomus ashlandi"/>
+        <filter val="Tropocyclops prasinus mexicanus"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="5">
     <mergeCell ref="U21:U22"/>
     <mergeCell ref="U23:U24"/>

--- a/data/raw/GLNPO 2024 Spring/Huron/D100/HU 48 D100 Spring 2024 24GH02I13 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Huron/D100/HU 48 D100 Spring 2024 24GH02I13 Zoop.xlsx
@@ -5,22 +5,19 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Huron\D100\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gllabuser\Desktop\GLNPO Sample Files\2024\Spring\Huron\D100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF464213-A2E7-4430-BCCA-9016EBDB76E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6409C7C4-4D1F-4952-9742-E473A4575C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7EC3FBA-13EF-49DD-99E1-5755DB56AABA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{B7EC3FBA-13EF-49DD-99E1-5755DB56AABA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$239</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <pivotCaches>
-    <pivotCache cacheId="37" r:id="rId2"/>
+    <pivotCache cacheId="0" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -42,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2966" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2980" uniqueCount="87">
   <si>
     <t>SAMPLENUM</t>
   </si>
@@ -309,7 +306,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -375,6 +372,18 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -518,7 +527,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -546,6 +555,11 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5423,7 +5437,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A67746FE-ED2C-48D4-B4EF-E6CF2CAC3DE8}" name="PivotTable2" cacheId="37" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A67746FE-ED2C-48D4-B4EF-E6CF2CAC3DE8}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="U1:AA19" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField showAll="0"/>
@@ -5885,21 +5899,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA400D11-AEBD-46C1-9BFD-0E6F8DC12898}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AA239"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="8" max="8" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="31.88671875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="6" bestFit="1" customWidth="1"/>
     <col min="24" max="25" width="3" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="2.88671875" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5961,7 +5974,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -6035,7 +6048,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -6103,7 +6116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -6168,7 +6181,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -6236,7 +6249,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -6301,7 +6314,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="7" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -6366,7 +6379,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -6434,7 +6447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -6499,7 +6512,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="10" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -6564,7 +6577,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -6629,7 +6642,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -6697,7 +6710,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -6768,7 +6781,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -6836,7 +6849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -6898,7 +6911,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -6969,7 +6982,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -7037,7 +7050,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -7105,7 +7118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -7179,7 +7192,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="20" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -7232,7 +7245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -7294,7 +7307,7 @@
         <v>1.002</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -7354,7 +7367,7 @@
         <v>1.0029999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -7416,7 +7429,7 @@
         <v>0.999</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -7476,7 +7489,7 @@
         <v>0.996</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -7536,7 +7549,7 @@
       </c>
       <c r="W25" s="14"/>
     </row>
-    <row r="26" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -7596,7 +7609,7 @@
       </c>
       <c r="W26" s="14"/>
     </row>
-    <row r="27" spans="1:27" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -7654,7 +7667,7 @@
       <c r="V27" s="13"/>
       <c r="W27" s="14"/>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -7707,7 +7720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -7760,7 +7773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -7813,7 +7826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -7866,7 +7879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -7919,7 +7932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -7972,7 +7985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -8025,7 +8038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -8078,7 +8091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -8131,7 +8144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -8184,7 +8197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -8237,7 +8250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -8290,7 +8303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -8343,7 +8356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -8396,7 +8409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -8449,7 +8462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -8502,7 +8515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -8555,7 +8568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -8608,7 +8621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -8661,7 +8674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -8714,7 +8727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -8767,7 +8780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -8820,7 +8833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -8873,7 +8886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -8926,7 +8939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -8979,7 +8992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -9032,7 +9045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -9079,13 +9092,13 @@
         <v>0.83799999999999997</v>
       </c>
       <c r="P54" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="Q54">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -9138,7 +9151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -9191,7 +9204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -9244,7 +9257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -9297,7 +9310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -9350,7 +9363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -9403,7 +9416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -9456,7 +9469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -9509,7 +9522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -9562,7 +9575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -9615,7 +9628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>18</v>
       </c>
@@ -9668,7 +9681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -9721,7 +9734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>18</v>
       </c>
@@ -9774,7 +9787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -9827,7 +9840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -9880,7 +9893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -9933,7 +9946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -9986,7 +9999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -10039,7 +10052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -10092,7 +10105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -10145,7 +10158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -10198,7 +10211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -10251,7 +10264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>18</v>
       </c>
@@ -10304,7 +10317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>18</v>
       </c>
@@ -10357,7 +10370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>18</v>
       </c>
@@ -10410,7 +10423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>18</v>
       </c>
@@ -10463,7 +10476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>18</v>
       </c>
@@ -10516,7 +10529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>18</v>
       </c>
@@ -10569,7 +10582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>18</v>
       </c>
@@ -10622,7 +10635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>18</v>
       </c>
@@ -10675,7 +10688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>18</v>
       </c>
@@ -10728,7 +10741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>18</v>
       </c>
@@ -10781,7 +10794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>18</v>
       </c>
@@ -10834,7 +10847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>18</v>
       </c>
@@ -10887,7 +10900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>18</v>
       </c>
@@ -10940,7 +10953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>18</v>
       </c>
@@ -10993,7 +11006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>18</v>
       </c>
@@ -11046,7 +11059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>18</v>
       </c>
@@ -11099,7 +11112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>18</v>
       </c>
@@ -11152,7 +11165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>18</v>
       </c>
@@ -11205,7 +11218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>18</v>
       </c>
@@ -11258,7 +11271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>18</v>
       </c>
@@ -11311,7 +11324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>18</v>
       </c>
@@ -11364,7 +11377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>18</v>
       </c>
@@ -11417,7 +11430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -11470,7 +11483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>18</v>
       </c>
@@ -11523,7 +11536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>18</v>
       </c>
@@ -11576,7 +11589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>18</v>
       </c>
@@ -11629,7 +11642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>18</v>
       </c>
@@ -11682,7 +11695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>18</v>
       </c>
@@ -11735,7 +11748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>18</v>
       </c>
@@ -11788,7 +11801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>18</v>
       </c>
@@ -11841,7 +11854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>18</v>
       </c>
@@ -11894,7 +11907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>18</v>
       </c>
@@ -11947,7 +11960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>18</v>
       </c>
@@ -12000,7 +12013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>18</v>
       </c>
@@ -12053,7 +12066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>18</v>
       </c>
@@ -12106,7 +12119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>18</v>
       </c>
@@ -12159,7 +12172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>18</v>
       </c>
@@ -12212,7 +12225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>18</v>
       </c>
@@ -12265,7 +12278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>18</v>
       </c>
@@ -12318,7 +12331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>18</v>
       </c>
@@ -12371,7 +12384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>18</v>
       </c>
@@ -12424,7 +12437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>18</v>
       </c>
@@ -12477,7 +12490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>18</v>
       </c>
@@ -12530,7 +12543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>18</v>
       </c>
@@ -12583,7 +12596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>18</v>
       </c>
@@ -12636,7 +12649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>18</v>
       </c>
@@ -12689,7 +12702,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="123" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>18</v>
       </c>
@@ -12742,7 +12755,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>18</v>
       </c>
@@ -12795,7 +12808,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>18</v>
       </c>
@@ -12848,7 +12861,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="126" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>18</v>
       </c>
@@ -12901,7 +12914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>18</v>
       </c>
@@ -12954,7 +12967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>18</v>
       </c>
@@ -13007,7 +13020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>18</v>
       </c>
@@ -13060,7 +13073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>18</v>
       </c>
@@ -13113,7 +13126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>18</v>
       </c>
@@ -13166,7 +13179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>18</v>
       </c>
@@ -13219,7 +13232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>18</v>
       </c>
@@ -13272,7 +13285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>18</v>
       </c>
@@ -13325,7 +13338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>18</v>
       </c>
@@ -13378,7 +13391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>18</v>
       </c>
@@ -13431,7 +13444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>18</v>
       </c>
@@ -13484,7 +13497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>18</v>
       </c>
@@ -13537,7 +13550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>18</v>
       </c>
@@ -13590,7 +13603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>18</v>
       </c>
@@ -13643,7 +13656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>18</v>
       </c>
@@ -13696,7 +13709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>18</v>
       </c>
@@ -13749,7 +13762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>18</v>
       </c>
@@ -13802,7 +13815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>18</v>
       </c>
@@ -13855,7 +13868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>18</v>
       </c>
@@ -13908,7 +13921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>18</v>
       </c>
@@ -13961,7 +13974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>18</v>
       </c>
@@ -14014,7 +14027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>18</v>
       </c>
@@ -14067,7 +14080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>18</v>
       </c>
@@ -14120,7 +14133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>18</v>
       </c>
@@ -14173,7 +14186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>18</v>
       </c>
@@ -14226,7 +14239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>18</v>
       </c>
@@ -14279,7 +14292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>18</v>
       </c>
@@ -14332,7 +14345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>18</v>
       </c>
@@ -14385,7 +14398,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="155" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>18</v>
       </c>
@@ -14438,7 +14451,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>18</v>
       </c>
@@ -14491,7 +14504,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>18</v>
       </c>
@@ -14544,7 +14557,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="158" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>18</v>
       </c>
@@ -14597,7 +14610,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="159" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>18</v>
       </c>
@@ -14650,7 +14663,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="160" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>18</v>
       </c>
@@ -14703,7 +14716,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>18</v>
       </c>
@@ -14756,7 +14769,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="162" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>18</v>
       </c>
@@ -14809,7 +14822,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="163" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>18</v>
       </c>
@@ -14862,7 +14875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>18</v>
       </c>
@@ -14915,7 +14928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>18</v>
       </c>
@@ -14968,7 +14981,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="166" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>18</v>
       </c>
@@ -15021,7 +15034,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>18</v>
       </c>
@@ -15074,7 +15087,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>18</v>
       </c>
@@ -15127,7 +15140,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="169" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>18</v>
       </c>
@@ -15180,7 +15193,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="170" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>18</v>
       </c>
@@ -15233,7 +15246,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="171" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>18</v>
       </c>
@@ -15286,7 +15299,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>18</v>
       </c>
@@ -15339,7 +15352,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="173" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>18</v>
       </c>
@@ -15392,7 +15405,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>18</v>
       </c>
@@ -15445,7 +15458,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="175" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>18</v>
       </c>
@@ -15498,7 +15511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>18</v>
       </c>
@@ -15551,7 +15564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>18</v>
       </c>
@@ -15604,7 +15617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>18</v>
       </c>
@@ -15657,7 +15670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>18</v>
       </c>
@@ -15710,7 +15723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>18</v>
       </c>
@@ -15763,7 +15776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>18</v>
       </c>
@@ -15816,7 +15829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>18</v>
       </c>
@@ -15863,13 +15876,13 @@
         <v>0.51600000000000001</v>
       </c>
       <c r="P182" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="Q182">
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>18</v>
       </c>
@@ -15922,7 +15935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>18</v>
       </c>
@@ -15975,7 +15988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>18</v>
       </c>
@@ -16028,7 +16041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>18</v>
       </c>
@@ -16081,7 +16094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>18</v>
       </c>
@@ -16134,7 +16147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>18</v>
       </c>
@@ -16187,7 +16200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>18</v>
       </c>
@@ -16240,7 +16253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>18</v>
       </c>
@@ -16293,7 +16306,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="191" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>18</v>
       </c>
@@ -16346,7 +16359,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>18</v>
       </c>
@@ -16399,7 +16412,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>18</v>
       </c>
@@ -16452,7 +16465,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="194" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>18</v>
       </c>
@@ -16505,7 +16518,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="195" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>18</v>
       </c>
@@ -16558,7 +16571,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="196" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>18</v>
       </c>
@@ -16611,7 +16624,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>18</v>
       </c>
@@ -16664,7 +16677,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="198" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>18</v>
       </c>
@@ -16717,7 +16730,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="199" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>18</v>
       </c>
@@ -16770,7 +16783,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="200" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>18</v>
       </c>
@@ -16823,7 +16836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>18</v>
       </c>
@@ -16876,7 +16889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>18</v>
       </c>
@@ -16929,7 +16942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>18</v>
       </c>
@@ -16982,7 +16995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>18</v>
       </c>
@@ -17035,7 +17048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>18</v>
       </c>
@@ -17088,7 +17101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>18</v>
       </c>
@@ -17141,7 +17154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>18</v>
       </c>
@@ -17194,7 +17207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>18</v>
       </c>
@@ -17247,7 +17260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>18</v>
       </c>
@@ -17300,7 +17313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>18</v>
       </c>
@@ -17353,7 +17366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>18</v>
       </c>
@@ -17406,7 +17419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>18</v>
       </c>
@@ -17459,7 +17472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>18</v>
       </c>
@@ -17512,7 +17525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>18</v>
       </c>
@@ -17565,7 +17578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>18</v>
       </c>
@@ -17618,7 +17631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>18</v>
       </c>
@@ -17671,7 +17684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>18</v>
       </c>
@@ -17724,7 +17737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>18</v>
       </c>
@@ -17777,7 +17790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>18</v>
       </c>
@@ -17830,7 +17843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>18</v>
       </c>
@@ -17883,7 +17896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>18</v>
       </c>
@@ -17936,7 +17949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>18</v>
       </c>
@@ -17989,7 +18002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>18</v>
       </c>
@@ -18042,7 +18055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>18</v>
       </c>
@@ -18095,7 +18108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>18</v>
       </c>
@@ -18148,7 +18161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>18</v>
       </c>
@@ -18201,7 +18214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>18</v>
       </c>
@@ -18254,113 +18267,113 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A228" t="s">
-        <v>18</v>
-      </c>
-      <c r="B228" t="s">
-        <v>19</v>
-      </c>
-      <c r="C228" t="s">
-        <v>20</v>
-      </c>
-      <c r="D228">
-        <v>-1</v>
-      </c>
-      <c r="E228" t="s">
-        <v>21</v>
-      </c>
-      <c r="F228">
-        <v>128</v>
-      </c>
-      <c r="G228" t="s">
-        <v>22</v>
-      </c>
-      <c r="H228" s="1">
-        <v>45580</v>
-      </c>
-      <c r="I228" t="s">
-        <v>23</v>
-      </c>
-      <c r="J228" t="s">
-        <v>24</v>
-      </c>
-      <c r="K228" s="3" t="s">
+    <row r="228" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A228" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B228" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C228" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D228" s="7">
+        <v>-1</v>
+      </c>
+      <c r="E228" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F228" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G228" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H228" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="I228" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J228" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K228" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="L228" s="3" t="s">
+      <c r="L228" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="M228" s="4" t="s">
+      <c r="M228" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="N228" s="4" t="s">
+      <c r="N228" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="O228" t="s">
+      <c r="O228" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="P228" t="s">
+      <c r="P228" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="Q228">
+      <c r="Q228" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A229" t="s">
-        <v>18</v>
-      </c>
-      <c r="B229" t="s">
-        <v>19</v>
-      </c>
-      <c r="C229" t="s">
-        <v>20</v>
-      </c>
-      <c r="D229">
-        <v>-1</v>
-      </c>
-      <c r="E229" t="s">
-        <v>56</v>
-      </c>
-      <c r="F229">
-        <v>128</v>
-      </c>
-      <c r="G229" t="s">
-        <v>22</v>
-      </c>
-      <c r="H229" s="1">
-        <v>45580</v>
-      </c>
-      <c r="I229" t="s">
-        <v>23</v>
-      </c>
-      <c r="J229" t="s">
-        <v>24</v>
-      </c>
-      <c r="K229" s="3" t="s">
+    <row r="229" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A229" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B229" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C229" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D229" s="7">
+        <v>-1</v>
+      </c>
+      <c r="E229" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F229" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G229" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H229" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="I229" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J229" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K229" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="L229" s="3" t="s">
+      <c r="L229" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="M229" s="4" t="s">
+      <c r="M229" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="N229" s="4" t="s">
+      <c r="N229" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="O229" t="s">
+      <c r="O229" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="P229" t="s">
+      <c r="P229" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="Q229">
+      <c r="Q229" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A230" s="7" t="s">
         <v>18</v>
       </c>
@@ -18376,8 +18389,8 @@
       <c r="E230" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="F230" s="7">
-        <v>64</v>
+      <c r="F230" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="G230" s="7" t="s">
         <v>22</v>
@@ -18413,7 +18426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A231" s="7" t="s">
         <v>18</v>
       </c>
@@ -18429,8 +18442,8 @@
       <c r="E231" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F231" s="7">
-        <v>128</v>
+      <c r="F231" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="G231" s="7" t="s">
         <v>22</v>
@@ -18466,7 +18479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A232" s="7" t="s">
         <v>18</v>
       </c>
@@ -18482,8 +18495,8 @@
       <c r="E232" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="F232" s="7">
-        <v>64</v>
+      <c r="F232" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="G232" s="7" t="s">
         <v>22</v>
@@ -18519,7 +18532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A233" s="7" t="s">
         <v>18</v>
       </c>
@@ -18535,8 +18548,8 @@
       <c r="E233" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F233" s="7">
-        <v>128</v>
+      <c r="F233" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="G233" s="7" t="s">
         <v>22</v>
@@ -18572,7 +18585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A234" s="7" t="s">
         <v>18</v>
       </c>
@@ -18588,8 +18601,8 @@
       <c r="E234" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="F234" s="7">
-        <v>64</v>
+      <c r="F234" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="G234" s="7" t="s">
         <v>22</v>
@@ -18625,7 +18638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A235" s="7" t="s">
         <v>18</v>
       </c>
@@ -18641,8 +18654,8 @@
       <c r="E235" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F235" s="7">
-        <v>128</v>
+      <c r="F235" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="G235" s="7" t="s">
         <v>22</v>
@@ -18678,7 +18691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A236" s="7" t="s">
         <v>18</v>
       </c>
@@ -18694,8 +18707,8 @@
       <c r="E236" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="F236" s="7">
-        <v>64</v>
+      <c r="F236" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="G236" s="7" t="s">
         <v>22</v>
@@ -18731,7 +18744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A237" s="7" t="s">
         <v>18</v>
       </c>
@@ -18747,8 +18760,8 @@
       <c r="E237" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F237" s="7">
-        <v>128</v>
+      <c r="F237" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="G237" s="7" t="s">
         <v>22</v>
@@ -18784,7 +18797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A238" s="7" t="s">
         <v>18</v>
       </c>
@@ -18800,8 +18813,8 @@
       <c r="E238" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="F238" s="7">
-        <v>64</v>
+      <c r="F238" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="G238" s="7" t="s">
         <v>22</v>
@@ -18837,7 +18850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A239" s="7" t="s">
         <v>18</v>
       </c>
@@ -18853,8 +18866,8 @@
       <c r="E239" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="F239" s="7">
-        <v>64</v>
+      <c r="F239" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="G239" s="7" t="s">
         <v>22</v>
@@ -18891,14 +18904,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R239" xr:uid="{DA400D11-AEBD-46C1-9BFD-0E6F8DC12898}">
-    <filterColumn colId="10">
-      <filters>
-        <filter val="Leptodiaptomus ashlandi"/>
-        <filter val="Tropocyclops prasinus mexicanus"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <mergeCells count="5">
     <mergeCell ref="U21:U22"/>
     <mergeCell ref="U23:U24"/>

--- a/data/raw/GLNPO 2024 Spring/Huron/D100/HU 48 D100 Spring 2024 24GH02I13 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Huron/D100/HU 48 D100 Spring 2024 24GH02I13 Zoop.xlsx
@@ -5,17 +5,20 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gllabuser\Desktop\GLNPO Sample Files\2024\Spring\Huron\D100\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Huron\D100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6409C7C4-4D1F-4952-9742-E473A4575C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6925AC0A-3F9C-4436-9C6E-ED5B3B067F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{B7EC3FBA-13EF-49DD-99E1-5755DB56AABA}"/>
+    <workbookView xWindow="780" yWindow="3204" windowWidth="17280" windowHeight="8880" xr2:uid="{B7EC3FBA-13EF-49DD-99E1-5755DB56AABA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$239</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId2"/>
   </pivotCaches>
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2980" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2968" uniqueCount="87">
   <si>
     <t>SAMPLENUM</t>
   </si>
@@ -543,6 +546,11 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -555,11 +563,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5899,20 +5902,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA400D11-AEBD-46C1-9BFD-0E6F8DC12898}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AA239"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="31.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="31.88671875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.88671875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="6" bestFit="1" customWidth="1"/>
     <col min="24" max="25" width="3" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="2.88671875" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5974,7 +5978,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -6048,7 +6052,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -6116,7 +6120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -6181,7 +6185,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -6249,7 +6253,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -6314,7 +6318,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -6379,7 +6383,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -6447,7 +6451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -6512,7 +6516,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -6577,7 +6581,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -6642,7 +6646,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -6710,7 +6714,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -6781,7 +6785,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -6849,7 +6853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -6911,7 +6915,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -6982,7 +6986,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -7050,7 +7054,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -7118,7 +7122,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -7192,7 +7196,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -7245,7 +7249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -7297,7 +7301,7 @@
       <c r="Q21">
         <v>1</v>
       </c>
-      <c r="U21" s="11" t="s">
+      <c r="U21" s="14" t="s">
         <v>79</v>
       </c>
       <c r="V21" s="8" t="s">
@@ -7307,7 +7311,7 @@
         <v>1.002</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -7359,7 +7363,7 @@
       <c r="Q22">
         <v>1</v>
       </c>
-      <c r="U22" s="12"/>
+      <c r="U22" s="15"/>
       <c r="V22" s="8" t="s">
         <v>80</v>
       </c>
@@ -7367,7 +7371,7 @@
         <v>1.0029999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -7419,7 +7423,7 @@
       <c r="Q23">
         <v>1</v>
       </c>
-      <c r="U23" s="11" t="s">
+      <c r="U23" s="14" t="s">
         <v>81</v>
       </c>
       <c r="V23" s="8" t="s">
@@ -7429,7 +7433,7 @@
         <v>0.999</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -7481,7 +7485,7 @@
       <c r="Q24">
         <v>1</v>
       </c>
-      <c r="U24" s="12"/>
+      <c r="U24" s="15"/>
       <c r="V24" s="8" t="s">
         <v>80</v>
       </c>
@@ -7489,7 +7493,7 @@
         <v>0.996</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -7544,12 +7548,12 @@
       <c r="U25" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="V25" s="13" t="s">
+      <c r="V25" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="W25" s="14"/>
-    </row>
-    <row r="26" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W25" s="17"/>
+    </row>
+    <row r="26" spans="1:27" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -7604,12 +7608,12 @@
       <c r="U26" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="V26" s="13" t="s">
+      <c r="V26" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="W26" s="14"/>
-    </row>
-    <row r="27" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W26" s="17"/>
+    </row>
+    <row r="27" spans="1:27" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -7664,10 +7668,10 @@
       <c r="U27" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="V27" s="13"/>
-      <c r="W27" s="14"/>
-    </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="V27" s="16"/>
+      <c r="W27" s="17"/>
+    </row>
+    <row r="28" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -7720,7 +7724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -7773,7 +7777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -7826,7 +7830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -7879,7 +7883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -7932,7 +7936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -7985,7 +7989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -8038,7 +8042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -8091,7 +8095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -8144,7 +8148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -8197,7 +8201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -8250,7 +8254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -8303,7 +8307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -8356,7 +8360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -8409,7 +8413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -8462,7 +8466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -8515,7 +8519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -8568,7 +8572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -8621,7 +8625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -8674,7 +8678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -8727,7 +8731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -8780,7 +8784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -8833,7 +8837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -8886,7 +8890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -8939,7 +8943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -8992,7 +8996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -9045,7 +9049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -9092,13 +9096,13 @@
         <v>0.83799999999999997</v>
       </c>
       <c r="P54" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="Q54">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -9151,7 +9155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -9204,7 +9208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -9257,7 +9261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -9310,7 +9314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -9363,7 +9367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -9416,7 +9420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -9469,7 +9473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -9522,7 +9526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -9575,7 +9579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -9628,7 +9632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>18</v>
       </c>
@@ -9681,7 +9685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -9734,7 +9738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>18</v>
       </c>
@@ -9787,7 +9791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -9840,7 +9844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -9893,7 +9897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -9946,7 +9950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -9999,7 +10003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -10052,7 +10056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -10105,7 +10109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -10158,7 +10162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -10211,7 +10215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -10264,7 +10268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>18</v>
       </c>
@@ -10317,7 +10321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>18</v>
       </c>
@@ -10370,7 +10374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>18</v>
       </c>
@@ -10423,7 +10427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>18</v>
       </c>
@@ -10476,7 +10480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>18</v>
       </c>
@@ -10529,7 +10533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>18</v>
       </c>
@@ -10582,7 +10586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>18</v>
       </c>
@@ -10635,7 +10639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>18</v>
       </c>
@@ -10688,7 +10692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>18</v>
       </c>
@@ -10741,7 +10745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>18</v>
       </c>
@@ -10794,7 +10798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>18</v>
       </c>
@@ -10847,7 +10851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>18</v>
       </c>
@@ -10900,7 +10904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>18</v>
       </c>
@@ -10953,7 +10957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>18</v>
       </c>
@@ -11006,7 +11010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>18</v>
       </c>
@@ -11059,7 +11063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>18</v>
       </c>
@@ -11112,7 +11116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>18</v>
       </c>
@@ -11165,7 +11169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>18</v>
       </c>
@@ -11218,7 +11222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>18</v>
       </c>
@@ -11271,7 +11275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>18</v>
       </c>
@@ -11324,7 +11328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>18</v>
       </c>
@@ -11377,7 +11381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>18</v>
       </c>
@@ -11430,7 +11434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -11483,7 +11487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>18</v>
       </c>
@@ -11536,7 +11540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>18</v>
       </c>
@@ -11589,7 +11593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>18</v>
       </c>
@@ -11642,7 +11646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>18</v>
       </c>
@@ -11695,7 +11699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>18</v>
       </c>
@@ -11748,7 +11752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>18</v>
       </c>
@@ -11801,7 +11805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>18</v>
       </c>
@@ -11854,7 +11858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>18</v>
       </c>
@@ -11907,7 +11911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>18</v>
       </c>
@@ -11960,7 +11964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>18</v>
       </c>
@@ -12013,7 +12017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>18</v>
       </c>
@@ -12066,7 +12070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>18</v>
       </c>
@@ -12119,7 +12123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>18</v>
       </c>
@@ -12172,7 +12176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>18</v>
       </c>
@@ -12225,7 +12229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>18</v>
       </c>
@@ -12278,7 +12282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>18</v>
       </c>
@@ -12331,7 +12335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>18</v>
       </c>
@@ -12384,7 +12388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>18</v>
       </c>
@@ -12437,7 +12441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>18</v>
       </c>
@@ -12490,7 +12494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>18</v>
       </c>
@@ -12543,7 +12547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>18</v>
       </c>
@@ -12596,7 +12600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>18</v>
       </c>
@@ -12649,7 +12653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>18</v>
       </c>
@@ -12702,7 +12706,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>18</v>
       </c>
@@ -12755,7 +12759,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>18</v>
       </c>
@@ -12808,7 +12812,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>18</v>
       </c>
@@ -12861,7 +12865,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>18</v>
       </c>
@@ -12914,7 +12918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>18</v>
       </c>
@@ -12967,7 +12971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>18</v>
       </c>
@@ -13020,7 +13024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>18</v>
       </c>
@@ -13073,7 +13077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>18</v>
       </c>
@@ -13126,7 +13130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>18</v>
       </c>
@@ -13179,7 +13183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>18</v>
       </c>
@@ -13232,7 +13236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>18</v>
       </c>
@@ -13285,7 +13289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>18</v>
       </c>
@@ -13338,7 +13342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>18</v>
       </c>
@@ -13391,7 +13395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>18</v>
       </c>
@@ -13444,7 +13448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>18</v>
       </c>
@@ -13497,7 +13501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>18</v>
       </c>
@@ -13550,7 +13554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>18</v>
       </c>
@@ -13603,7 +13607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>18</v>
       </c>
@@ -13656,7 +13660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>18</v>
       </c>
@@ -13709,7 +13713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>18</v>
       </c>
@@ -13762,7 +13766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>18</v>
       </c>
@@ -13815,7 +13819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>18</v>
       </c>
@@ -13868,7 +13872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>18</v>
       </c>
@@ -13921,7 +13925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>18</v>
       </c>
@@ -13974,7 +13978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>18</v>
       </c>
@@ -14027,7 +14031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>18</v>
       </c>
@@ -14080,7 +14084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>18</v>
       </c>
@@ -14133,7 +14137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>18</v>
       </c>
@@ -14186,7 +14190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>18</v>
       </c>
@@ -14239,7 +14243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>18</v>
       </c>
@@ -14292,7 +14296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>18</v>
       </c>
@@ -14345,7 +14349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>18</v>
       </c>
@@ -14398,7 +14402,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>18</v>
       </c>
@@ -14451,7 +14455,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>18</v>
       </c>
@@ -14504,7 +14508,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>18</v>
       </c>
@@ -14557,7 +14561,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>18</v>
       </c>
@@ -14610,7 +14614,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>18</v>
       </c>
@@ -14663,7 +14667,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>18</v>
       </c>
@@ -14716,7 +14720,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>18</v>
       </c>
@@ -14769,7 +14773,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>18</v>
       </c>
@@ -14822,7 +14826,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>18</v>
       </c>
@@ -14875,7 +14879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>18</v>
       </c>
@@ -14928,7 +14932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>18</v>
       </c>
@@ -14981,7 +14985,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>18</v>
       </c>
@@ -15034,7 +15038,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>18</v>
       </c>
@@ -15087,7 +15091,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>18</v>
       </c>
@@ -15140,7 +15144,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>18</v>
       </c>
@@ -15193,7 +15197,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>18</v>
       </c>
@@ -15246,7 +15250,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>18</v>
       </c>
@@ -15299,7 +15303,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>18</v>
       </c>
@@ -15352,7 +15356,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>18</v>
       </c>
@@ -15405,7 +15409,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>18</v>
       </c>
@@ -15458,7 +15462,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>18</v>
       </c>
@@ -15511,7 +15515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>18</v>
       </c>
@@ -15564,7 +15568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>18</v>
       </c>
@@ -15617,7 +15621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>18</v>
       </c>
@@ -15670,7 +15674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>18</v>
       </c>
@@ -15723,7 +15727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>18</v>
       </c>
@@ -15776,7 +15780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>18</v>
       </c>
@@ -15829,7 +15833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>18</v>
       </c>
@@ -15876,13 +15880,13 @@
         <v>0.51600000000000001</v>
       </c>
       <c r="P182" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="Q182">
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>18</v>
       </c>
@@ -15935,7 +15939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>18</v>
       </c>
@@ -15988,7 +15992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>18</v>
       </c>
@@ -16041,7 +16045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>18</v>
       </c>
@@ -16094,7 +16098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>18</v>
       </c>
@@ -16147,7 +16151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>18</v>
       </c>
@@ -16200,7 +16204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>18</v>
       </c>
@@ -16253,7 +16257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>18</v>
       </c>
@@ -16306,7 +16310,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>18</v>
       </c>
@@ -16359,7 +16363,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>18</v>
       </c>
@@ -16412,7 +16416,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>18</v>
       </c>
@@ -16465,7 +16469,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>18</v>
       </c>
@@ -16518,7 +16522,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>18</v>
       </c>
@@ -16571,7 +16575,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>18</v>
       </c>
@@ -16624,7 +16628,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>18</v>
       </c>
@@ -16677,7 +16681,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>18</v>
       </c>
@@ -16730,7 +16734,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>18</v>
       </c>
@@ -16783,7 +16787,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>18</v>
       </c>
@@ -16836,7 +16840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>18</v>
       </c>
@@ -16889,7 +16893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>18</v>
       </c>
@@ -16942,7 +16946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>18</v>
       </c>
@@ -16995,7 +16999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>18</v>
       </c>
@@ -17048,7 +17052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>18</v>
       </c>
@@ -17101,7 +17105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>18</v>
       </c>
@@ -17154,7 +17158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>18</v>
       </c>
@@ -17207,7 +17211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>18</v>
       </c>
@@ -17260,7 +17264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>18</v>
       </c>
@@ -17313,7 +17317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>18</v>
       </c>
@@ -17366,7 +17370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>18</v>
       </c>
@@ -17419,7 +17423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>18</v>
       </c>
@@ -17472,7 +17476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>18</v>
       </c>
@@ -17525,7 +17529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>18</v>
       </c>
@@ -17578,7 +17582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>18</v>
       </c>
@@ -17631,7 +17635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>18</v>
       </c>
@@ -17684,7 +17688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>18</v>
       </c>
@@ -17737,7 +17741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>18</v>
       </c>
@@ -17790,7 +17794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>18</v>
       </c>
@@ -17843,7 +17847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>18</v>
       </c>
@@ -17896,7 +17900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>18</v>
       </c>
@@ -17949,7 +17953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>18</v>
       </c>
@@ -18002,7 +18006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>18</v>
       </c>
@@ -18055,7 +18059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>18</v>
       </c>
@@ -18108,7 +18112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>18</v>
       </c>
@@ -18161,7 +18165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>18</v>
       </c>
@@ -18214,7 +18218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>18</v>
       </c>
@@ -18267,7 +18271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:17" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="7" t="s">
         <v>18</v>
       </c>
@@ -18281,33 +18285,33 @@
         <v>-1</v>
       </c>
       <c r="E228" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F228" s="7">
+        <v>128</v>
+      </c>
+      <c r="G228" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H228" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F228" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G228" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H228" s="15" t="s">
-        <v>38</v>
-      </c>
       <c r="I228" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J228" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="K228" s="16" t="s">
+      <c r="K228" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="L228" s="16" t="s">
+      <c r="L228" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="M228" s="17" t="s">
+      <c r="M228" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="N228" s="17" t="s">
+      <c r="N228" s="13" t="s">
         <v>59</v>
       </c>
       <c r="O228" s="7" t="s">
@@ -18320,7 +18324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:17" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="7" t="s">
         <v>18</v>
       </c>
@@ -18334,33 +18338,33 @@
         <v>-1</v>
       </c>
       <c r="E229" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F229" s="7">
+        <v>128</v>
+      </c>
+      <c r="G229" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H229" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F229" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G229" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H229" s="15" t="s">
-        <v>38</v>
-      </c>
       <c r="I229" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J229" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="K229" s="16" t="s">
+      <c r="K229" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="L229" s="16" t="s">
+      <c r="L229" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="M229" s="17" t="s">
+      <c r="M229" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="N229" s="17" t="s">
+      <c r="N229" s="13" t="s">
         <v>59</v>
       </c>
       <c r="O229" s="7" t="s">
@@ -18373,7 +18377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="7" t="s">
         <v>18</v>
       </c>
@@ -18389,8 +18393,8 @@
       <c r="E230" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="F230" s="7" t="s">
-        <v>38</v>
+      <c r="F230" s="7">
+        <v>64</v>
       </c>
       <c r="G230" s="7" t="s">
         <v>22</v>
@@ -18426,7 +18430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="7" t="s">
         <v>18</v>
       </c>
@@ -18442,8 +18446,8 @@
       <c r="E231" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F231" s="7" t="s">
-        <v>38</v>
+      <c r="F231" s="7">
+        <v>128</v>
       </c>
       <c r="G231" s="7" t="s">
         <v>22</v>
@@ -18479,7 +18483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="7" t="s">
         <v>18</v>
       </c>
@@ -18495,8 +18499,8 @@
       <c r="E232" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="F232" s="7" t="s">
-        <v>38</v>
+      <c r="F232" s="7">
+        <v>64</v>
       </c>
       <c r="G232" s="7" t="s">
         <v>22</v>
@@ -18532,7 +18536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="7" t="s">
         <v>18</v>
       </c>
@@ -18548,8 +18552,8 @@
       <c r="E233" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F233" s="7" t="s">
-        <v>38</v>
+      <c r="F233" s="7">
+        <v>128</v>
       </c>
       <c r="G233" s="7" t="s">
         <v>22</v>
@@ -18585,7 +18589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="7" t="s">
         <v>18</v>
       </c>
@@ -18601,8 +18605,8 @@
       <c r="E234" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="F234" s="7" t="s">
-        <v>38</v>
+      <c r="F234" s="7">
+        <v>64</v>
       </c>
       <c r="G234" s="7" t="s">
         <v>22</v>
@@ -18638,7 +18642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="7" t="s">
         <v>18</v>
       </c>
@@ -18654,8 +18658,8 @@
       <c r="E235" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F235" s="7" t="s">
-        <v>38</v>
+      <c r="F235" s="7">
+        <v>128</v>
       </c>
       <c r="G235" s="7" t="s">
         <v>22</v>
@@ -18691,7 +18695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="7" t="s">
         <v>18</v>
       </c>
@@ -18707,8 +18711,8 @@
       <c r="E236" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="F236" s="7" t="s">
-        <v>38</v>
+      <c r="F236" s="7">
+        <v>64</v>
       </c>
       <c r="G236" s="7" t="s">
         <v>22</v>
@@ -18744,7 +18748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A237" s="7" t="s">
         <v>18</v>
       </c>
@@ -18760,8 +18764,8 @@
       <c r="E237" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F237" s="7" t="s">
-        <v>38</v>
+      <c r="F237" s="7">
+        <v>128</v>
       </c>
       <c r="G237" s="7" t="s">
         <v>22</v>
@@ -18797,7 +18801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A238" s="7" t="s">
         <v>18</v>
       </c>
@@ -18813,8 +18817,8 @@
       <c r="E238" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="F238" s="7" t="s">
-        <v>38</v>
+      <c r="F238" s="7">
+        <v>64</v>
       </c>
       <c r="G238" s="7" t="s">
         <v>22</v>
@@ -18850,7 +18854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="7" t="s">
         <v>18</v>
       </c>
@@ -18866,8 +18870,8 @@
       <c r="E239" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="F239" s="7" t="s">
-        <v>38</v>
+      <c r="F239" s="7">
+        <v>64</v>
       </c>
       <c r="G239" s="7" t="s">
         <v>22</v>
@@ -18904,6 +18908,19 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R239" xr:uid="{DA400D11-AEBD-46C1-9BFD-0E6F8DC12898}">
+    <filterColumn colId="10">
+      <filters>
+        <filter val="Leptodiaptomus ashlandi"/>
+        <filter val="Tropocyclops prasinus mexicanus"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="15">
+      <filters>
+        <filter val="NA"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="5">
     <mergeCell ref="U21:U22"/>
     <mergeCell ref="U23:U24"/>

--- a/data/raw/GLNPO 2024 Spring/Huron/D100/HU 48 D100 Spring 2024 24GH02I13 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Huron/D100/HU 48 D100 Spring 2024 24GH02I13 Zoop.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Huron\D100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6925AC0A-3F9C-4436-9C6E-ED5B3B067F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F94DB9-C300-4D8C-B579-A23BD1CC6335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="3204" windowWidth="17280" windowHeight="8880" xr2:uid="{B7EC3FBA-13EF-49DD-99E1-5755DB56AABA}"/>
+    <workbookView xWindow="1164" yWindow="5160" windowWidth="17280" windowHeight="8880" xr2:uid="{B7EC3FBA-13EF-49DD-99E1-5755DB56AABA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId2"/>
+    <pivotCache cacheId="2" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -5440,7 +5440,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A67746FE-ED2C-48D4-B4EF-E6CF2CAC3DE8}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A67746FE-ED2C-48D4-B4EF-E6CF2CAC3DE8}" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="U1:AA19" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField showAll="0"/>
@@ -9049,7 +9049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -15833,7 +15833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>18</v>
       </c>
@@ -17158,7 +17158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>18</v>
       </c>
@@ -17196,10 +17196,10 @@
         <v>69</v>
       </c>
       <c r="M207" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="N207" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="N207" s="4" t="s">
-        <v>59</v>
       </c>
       <c r="O207">
         <v>0.625</v>
@@ -17248,8 +17248,8 @@
       <c r="L208" t="s">
         <v>51</v>
       </c>
-      <c r="M208" t="s">
-        <v>32</v>
+      <c r="M208" s="13" t="s">
+        <v>59</v>
       </c>
       <c r="N208" t="s">
         <v>28</v>
@@ -17301,8 +17301,8 @@
       <c r="L209" t="s">
         <v>51</v>
       </c>
-      <c r="M209" t="s">
-        <v>32</v>
+      <c r="M209" s="13" t="s">
+        <v>59</v>
       </c>
       <c r="N209" t="s">
         <v>28</v>
@@ -18271,7 +18271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:17" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A228" s="7" t="s">
         <v>18</v>
       </c>
@@ -18309,10 +18309,10 @@
         <v>69</v>
       </c>
       <c r="M228" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="N228" s="13" t="s">
         <v>49</v>
-      </c>
-      <c r="N228" s="13" t="s">
-        <v>59</v>
       </c>
       <c r="O228" s="7" t="s">
         <v>38</v>
@@ -18324,7 +18324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:17" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A229" s="7" t="s">
         <v>18</v>
       </c>
@@ -18362,10 +18362,10 @@
         <v>69</v>
       </c>
       <c r="M229" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="N229" s="13" t="s">
         <v>49</v>
-      </c>
-      <c r="N229" s="13" t="s">
-        <v>59</v>
       </c>
       <c r="O229" s="7" t="s">
         <v>38</v>
@@ -18748,7 +18748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="7" t="s">
         <v>18</v>
       </c>
@@ -18801,7 +18801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="7" t="s">
         <v>18</v>
       </c>
@@ -18909,10 +18909,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:R239" xr:uid="{DA400D11-AEBD-46C1-9BFD-0E6F8DC12898}">
-    <filterColumn colId="10">
+    <filterColumn colId="13">
       <filters>
-        <filter val="Leptodiaptomus ashlandi"/>
-        <filter val="Tropocyclops prasinus mexicanus"/>
+        <filter val="NDAP"/>
       </filters>
     </filterColumn>
     <filterColumn colId="15">
